--- a/lista_automatów.xlsx
+++ b/lista_automatów.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studmsugedupl-my.sharepoint.com/personal/a_mazur_177_studms_ug_edu_pl/Documents/Dokumenty/Praca/P&amp;L/PiL_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{295CA4DA-EC0E-4D8B-83A9-AB683910DE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{724D0C00-F88B-4E03-A390-6E93293660E0}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{295CA4DA-EC0E-4D8B-83A9-AB683910DE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9F95D72-4A38-4BCC-873B-77257B4F839E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{61DB3D85-53D2-4095-8488-275B522E96CE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="584">
   <si>
     <t>LP</t>
   </si>
@@ -1769,13 +1769,16 @@
   </si>
   <si>
     <t>Owner</t>
+  </si>
+  <si>
+    <t>tunel dworca od ul. Suchej, 50-085 Wrocław</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1961,8 +1964,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2166,8 +2179,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2282,6 +2301,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2328,7 +2362,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="42" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2371,6 +2405,9 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0" xfId="42" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2748,11 +2785,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2408DAD-1E50-448F-983F-1D2612F23BE6}">
-  <dimension ref="A1:AE155"/>
+  <dimension ref="A1:AE156"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -5321,23 +5358,14 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>42</v>
-      </c>
       <c r="B47">
-        <v>1210</v>
-      </c>
-      <c r="C47">
-        <v>3</v>
+        <v>1209</v>
       </c>
       <c r="D47" t="s">
         <v>196</v>
       </c>
-      <c r="E47" t="s">
-        <v>31</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>467</v>
+      <c r="F47" s="15" t="s">
+        <v>583</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>468</v>
@@ -5345,49 +5373,28 @@
       <c r="H47" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="I47" t="s">
-        <v>47</v>
-      </c>
-      <c r="J47" t="s">
-        <v>214</v>
-      </c>
-      <c r="K47" t="s">
-        <v>35</v>
-      </c>
-      <c r="L47" t="s">
-        <v>215</v>
-      </c>
-      <c r="M47" t="s">
-        <v>216</v>
-      </c>
-      <c r="P47" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>38</v>
-      </c>
-      <c r="S47" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>203</v>
+        <v>196</v>
+      </c>
+      <c r="E48" t="s">
+        <v>31</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>217</v>
+        <v>467</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>218</v>
+        <v>468</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>469</v>
@@ -5396,27 +5403,33 @@
         <v>47</v>
       </c>
       <c r="J48" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="K48" t="s">
-        <v>220</v>
-      </c>
-      <c r="L48">
-        <v>2100497500</v>
-      </c>
-      <c r="M48">
-        <v>24202094</v>
+        <v>35</v>
+      </c>
+      <c r="L48" t="s">
+        <v>215</v>
+      </c>
+      <c r="M48" t="s">
+        <v>216</v>
+      </c>
+      <c r="P48" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>38</v>
       </c>
       <c r="S48" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="49" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B49">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -5424,14 +5437,11 @@
       <c r="D49" t="s">
         <v>203</v>
       </c>
-      <c r="E49" t="s">
-        <v>31</v>
-      </c>
       <c r="F49" s="4" t="s">
-        <v>511</v>
+        <v>217</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>512</v>
+        <v>218</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>469</v>
@@ -5440,36 +5450,27 @@
         <v>47</v>
       </c>
       <c r="J49" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K49" t="s">
-        <v>35</v>
-      </c>
-      <c r="L49" t="s">
-        <v>222</v>
-      </c>
-      <c r="M49" t="s">
-        <v>223</v>
-      </c>
-      <c r="N49" t="s">
-        <v>224</v>
-      </c>
-      <c r="P49" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>38</v>
+        <v>220</v>
+      </c>
+      <c r="L49">
+        <v>2100497500</v>
+      </c>
+      <c r="M49">
+        <v>24202094</v>
       </c>
       <c r="S49" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B50">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -5481,10 +5482,10 @@
         <v>31</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>469</v>
@@ -5493,19 +5494,19 @@
         <v>47</v>
       </c>
       <c r="J50" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="K50" t="s">
         <v>35</v>
       </c>
       <c r="L50" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="M50" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N50" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="P50" t="s">
         <v>38</v>
@@ -5516,13 +5517,13 @@
       <c r="S50" t="s">
         <v>38</v>
       </c>
-      <c r="T50" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>45</v>
+      </c>
       <c r="B51">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -5534,39 +5535,48 @@
         <v>31</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>229</v>
+        <v>513</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>230</v>
+        <v>514</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>231</v>
+        <v>469</v>
       </c>
       <c r="I51" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J51" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="K51" t="s">
-        <v>220</v>
-      </c>
-      <c r="L51">
-        <v>2100778991</v>
-      </c>
-      <c r="M51">
-        <v>29259218</v>
+        <v>35</v>
+      </c>
+      <c r="L51" t="s">
+        <v>226</v>
+      </c>
+      <c r="M51" t="s">
+        <v>227</v>
+      </c>
+      <c r="N51" t="s">
+        <v>228</v>
       </c>
       <c r="P51" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="52" spans="1:24" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>47</v>
-      </c>
+      <c r="Q51" t="s">
+        <v>38</v>
+      </c>
+      <c r="S51" t="s">
+        <v>38</v>
+      </c>
+      <c r="T51" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B52">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -5578,45 +5588,39 @@
         <v>31</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I52" t="s">
-        <v>236</v>
+        <v>43</v>
       </c>
       <c r="J52" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="K52" t="s">
-        <v>35</v>
-      </c>
-      <c r="L52" t="s">
-        <v>238</v>
-      </c>
-      <c r="M52" t="s">
-        <v>239</v>
-      </c>
-      <c r="N52" t="s">
-        <v>240</v>
+        <v>220</v>
+      </c>
+      <c r="L52">
+        <v>2100778991</v>
+      </c>
+      <c r="M52">
+        <v>29259218</v>
       </c>
       <c r="P52" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q52" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B53">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -5628,31 +5632,31 @@
         <v>31</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>515</v>
+        <v>233</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>516</v>
+        <v>235</v>
       </c>
       <c r="I53" t="s">
-        <v>33</v>
+        <v>236</v>
       </c>
       <c r="J53" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="K53" t="s">
         <v>35</v>
       </c>
       <c r="L53" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="M53" t="s">
-        <v>183</v>
+        <v>239</v>
       </c>
       <c r="N53" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P53" t="s">
         <v>38</v>
@@ -5660,52 +5664,49 @@
       <c r="Q53" t="s">
         <v>38</v>
       </c>
-      <c r="W53">
-        <v>130076353</v>
-      </c>
-      <c r="X53" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B54">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="E54" t="s">
         <v>31</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>246</v>
+        <v>515</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>54</v>
+        <v>516</v>
       </c>
       <c r="I54" t="s">
-        <v>248</v>
+        <v>33</v>
       </c>
       <c r="J54" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="K54" t="s">
-        <v>220</v>
-      </c>
-      <c r="L54">
-        <v>2100453792</v>
-      </c>
-      <c r="M54">
-        <v>24201576</v>
+        <v>35</v>
+      </c>
+      <c r="L54" t="s">
+        <v>243</v>
+      </c>
+      <c r="M54" t="s">
+        <v>183</v>
+      </c>
+      <c r="N54" t="s">
+        <v>244</v>
       </c>
       <c r="P54" t="s">
         <v>38</v>
@@ -5713,16 +5714,19 @@
       <c r="Q54" t="s">
         <v>38</v>
       </c>
-      <c r="U54" t="s">
-        <v>38</v>
+      <c r="W54">
+        <v>130076353</v>
+      </c>
+      <c r="X54" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B55">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="C55">
         <v>3</v>
@@ -5734,142 +5738,148 @@
         <v>31</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>517</v>
+        <v>246</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>518</v>
+        <v>247</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="I55" t="s">
-        <v>72</v>
+        <v>248</v>
       </c>
       <c r="J55" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K55" t="s">
         <v>220</v>
       </c>
       <c r="L55">
-        <v>2100453814</v>
+        <v>2100453792</v>
       </c>
       <c r="M55">
-        <v>24221571</v>
+        <v>24201576</v>
       </c>
       <c r="P55" t="s">
         <v>38</v>
       </c>
       <c r="Q55" t="s">
+        <v>38</v>
+      </c>
+      <c r="U55" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B56">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>203</v>
+        <v>196</v>
+      </c>
+      <c r="E56" t="s">
+        <v>31</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>469</v>
+        <v>71</v>
       </c>
       <c r="I56" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="J56" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K56" t="s">
-        <v>35</v>
-      </c>
-      <c r="L56" t="s">
-        <v>252</v>
-      </c>
-      <c r="M56" t="s">
-        <v>253</v>
-      </c>
-      <c r="N56" t="s">
-        <v>254</v>
-      </c>
-      <c r="S56" t="s">
+        <v>220</v>
+      </c>
+      <c r="L56">
+        <v>2100453814</v>
+      </c>
+      <c r="M56">
+        <v>24221571</v>
+      </c>
+      <c r="P56" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q56" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B57">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C57">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>71</v>
+        <v>469</v>
       </c>
       <c r="I57" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="J57" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="K57" t="s">
-        <v>220</v>
-      </c>
-      <c r="L57">
-        <v>2100453798</v>
-      </c>
-      <c r="M57">
-        <v>24201588</v>
-      </c>
-      <c r="Q57" t="s">
+        <v>35</v>
+      </c>
+      <c r="L57" t="s">
+        <v>252</v>
+      </c>
+      <c r="M57" t="s">
+        <v>253</v>
+      </c>
+      <c r="N57" t="s">
+        <v>254</v>
+      </c>
+      <c r="S57" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B58">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C58">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D58" t="s">
         <v>196</v>
       </c>
-      <c r="E58" t="s">
-        <v>31</v>
-      </c>
       <c r="F58" s="4" t="s">
-        <v>256</v>
+        <v>521</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>257</v>
+        <v>522</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>71</v>
@@ -5878,19 +5888,16 @@
         <v>72</v>
       </c>
       <c r="J58" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="K58" t="s">
         <v>220</v>
       </c>
       <c r="L58">
-        <v>2100453758</v>
+        <v>2100453798</v>
       </c>
       <c r="M58">
-        <v>24234865</v>
-      </c>
-      <c r="P58" t="s">
-        <v>38</v>
+        <v>24201588</v>
       </c>
       <c r="Q58" t="s">
         <v>38</v>
@@ -5898,22 +5905,25 @@
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B59">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="C59">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D59" t="s">
         <v>196</v>
       </c>
-      <c r="F59" s="12" t="s">
-        <v>523</v>
+      <c r="E59" t="s">
+        <v>31</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>256</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>524</v>
+        <v>257</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>71</v>
@@ -5922,16 +5932,19 @@
         <v>72</v>
       </c>
       <c r="J59" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K59" t="s">
         <v>220</v>
       </c>
       <c r="L59">
-        <v>2100453770</v>
+        <v>2100453758</v>
       </c>
       <c r="M59">
-        <v>24234866</v>
+        <v>24234865</v>
+      </c>
+      <c r="P59" t="s">
+        <v>38</v>
       </c>
       <c r="Q59" t="s">
         <v>38</v>
@@ -5939,46 +5952,40 @@
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B60">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C60">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D60" t="s">
         <v>196</v>
       </c>
-      <c r="E60" t="s">
-        <v>31</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>525</v>
+      <c r="F60" s="12" t="s">
+        <v>523</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I60" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="J60" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K60" t="s">
         <v>220</v>
       </c>
       <c r="L60">
-        <v>2100453403</v>
+        <v>2100453770</v>
       </c>
       <c r="M60">
-        <v>24236382</v>
-      </c>
-      <c r="P60" t="s">
-        <v>38</v>
+        <v>24234866</v>
       </c>
       <c r="Q60" t="s">
         <v>38</v>
@@ -5986,10 +5993,10 @@
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B61">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C61">
         <v>3</v>
@@ -6001,28 +6008,28 @@
         <v>31</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>261</v>
+        <v>525</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>262</v>
+        <v>526</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>466</v>
+        <v>77</v>
       </c>
       <c r="I61" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="J61" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="K61" t="s">
         <v>220</v>
       </c>
       <c r="L61">
-        <v>2100453762</v>
+        <v>2100453403</v>
       </c>
       <c r="M61">
-        <v>24234868</v>
+        <v>24236382</v>
       </c>
       <c r="P61" t="s">
         <v>38</v>
@@ -6031,139 +6038,136 @@
         <v>38</v>
       </c>
     </row>
-    <row r="62" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B62">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="E62" t="s">
         <v>31</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>516</v>
+        <v>466</v>
       </c>
       <c r="I62" t="s">
         <v>33</v>
       </c>
       <c r="J62" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="K62" t="s">
         <v>220</v>
       </c>
       <c r="L62">
-        <v>2100453746</v>
+        <v>2100453762</v>
       </c>
       <c r="M62">
-        <v>24201541</v>
+        <v>24234868</v>
       </c>
       <c r="P62" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Q62" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B63">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="C63">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D63" t="s">
         <v>203</v>
       </c>
+      <c r="E63" t="s">
+        <v>31</v>
+      </c>
       <c r="F63" s="4" t="s">
-        <v>527</v>
+        <v>264</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>528</v>
+        <v>265</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>469</v>
+        <v>516</v>
       </c>
       <c r="I63" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="J63" t="s">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="K63" t="s">
-        <v>35</v>
-      </c>
-      <c r="L63" t="s">
-        <v>267</v>
-      </c>
-      <c r="M63" t="s">
-        <v>268</v>
-      </c>
-      <c r="N63" t="s">
-        <v>269</v>
-      </c>
-      <c r="S63" t="s">
+        <v>220</v>
+      </c>
+      <c r="L63">
+        <v>2100453746</v>
+      </c>
+      <c r="M63">
+        <v>24201541</v>
+      </c>
+      <c r="P63" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B64">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D64" t="s">
-        <v>196</v>
-      </c>
-      <c r="E64" t="s">
-        <v>31</v>
+        <v>203</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>231</v>
+        <v>469</v>
       </c>
       <c r="I64" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J64" t="s">
-        <v>270</v>
+        <v>190</v>
       </c>
       <c r="K64" t="s">
-        <v>220</v>
-      </c>
-      <c r="L64">
-        <v>2100453811</v>
-      </c>
-      <c r="M64">
-        <v>24201594</v>
-      </c>
-      <c r="P64" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="L64" t="s">
+        <v>267</v>
+      </c>
+      <c r="M64" t="s">
+        <v>268</v>
+      </c>
+      <c r="N64" t="s">
+        <v>269</v>
       </c>
       <c r="S64" t="s">
         <v>38</v>
@@ -6171,10 +6175,10 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B65">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="C65">
         <v>3</v>
@@ -6186,28 +6190,28 @@
         <v>31</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>470</v>
+        <v>529</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>42</v>
+        <v>231</v>
       </c>
       <c r="I65" t="s">
         <v>43</v>
       </c>
       <c r="J65" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K65" t="s">
-        <v>35</v>
-      </c>
-      <c r="L65" t="s">
-        <v>272</v>
-      </c>
-      <c r="M65" t="s">
-        <v>273</v>
+        <v>220</v>
+      </c>
+      <c r="L65">
+        <v>2100453811</v>
+      </c>
+      <c r="M65">
+        <v>24201594</v>
       </c>
       <c r="P65" t="s">
         <v>38</v>
@@ -6215,119 +6219,113 @@
       <c r="Q65" t="s">
         <v>38</v>
       </c>
-      <c r="T65" t="s">
-        <v>38</v>
-      </c>
-      <c r="U65" t="s">
+      <c r="S65" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B66">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="C66">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D66" t="s">
         <v>196</v>
       </c>
+      <c r="E66" t="s">
+        <v>31</v>
+      </c>
       <c r="F66" s="4" t="s">
-        <v>274</v>
+        <v>470</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>275</v>
+        <v>531</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="I66" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="J66" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="K66" t="s">
         <v>35</v>
       </c>
       <c r="L66" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="M66" t="s">
-        <v>278</v>
-      </c>
-      <c r="N66" t="s">
-        <v>279</v>
+        <v>273</v>
+      </c>
+      <c r="P66" t="s">
+        <v>38</v>
       </c>
       <c r="Q66" t="s">
+        <v>38</v>
+      </c>
+      <c r="T66" t="s">
+        <v>38</v>
+      </c>
+      <c r="U66" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B67">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D67" t="s">
         <v>196</v>
       </c>
-      <c r="E67" t="s">
-        <v>31</v>
-      </c>
       <c r="F67" s="4" t="s">
-        <v>470</v>
+        <v>274</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>471</v>
+        <v>275</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="I67" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="J67" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="K67" t="s">
         <v>35</v>
       </c>
       <c r="L67" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="M67" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="N67" t="s">
-        <v>283</v>
-      </c>
-      <c r="P67" t="s">
-        <v>38</v>
+        <v>279</v>
       </c>
       <c r="Q67" t="s">
-        <v>38</v>
-      </c>
-      <c r="T67" t="s">
-        <v>38</v>
-      </c>
-      <c r="U67" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B68">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C68">
         <v>3</v>
@@ -6351,10 +6349,19 @@
         <v>43</v>
       </c>
       <c r="J68" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="K68" t="s">
-        <v>220</v>
+        <v>35</v>
+      </c>
+      <c r="L68" t="s">
+        <v>281</v>
+      </c>
+      <c r="M68" t="s">
+        <v>282</v>
+      </c>
+      <c r="N68" t="s">
+        <v>283</v>
       </c>
       <c r="P68" t="s">
         <v>38</v>
@@ -6371,10 +6378,10 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B69">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C69">
         <v>3</v>
@@ -6398,16 +6405,10 @@
         <v>43</v>
       </c>
       <c r="J69" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K69" t="s">
-        <v>286</v>
-      </c>
-      <c r="L69">
-        <v>2100453778</v>
-      </c>
-      <c r="M69">
-        <v>24201572</v>
+        <v>220</v>
       </c>
       <c r="P69" t="s">
         <v>38</v>
@@ -6423,8 +6424,11 @@
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>65</v>
+      </c>
       <c r="B70">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C70">
         <v>3</v>
@@ -6448,16 +6452,16 @@
         <v>43</v>
       </c>
       <c r="J70" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K70" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="L70">
-        <v>2100453784</v>
+        <v>2100453778</v>
       </c>
       <c r="M70">
-        <v>24201579</v>
+        <v>24201572</v>
       </c>
       <c r="P70" t="s">
         <v>38</v>
@@ -6473,11 +6477,8 @@
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>67</v>
-      </c>
       <c r="B71">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C71">
         <v>3</v>
@@ -6485,11 +6486,14 @@
       <c r="D71" t="s">
         <v>196</v>
       </c>
+      <c r="E71" t="s">
+        <v>31</v>
+      </c>
       <c r="F71" s="4" t="s">
-        <v>288</v>
+        <v>470</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>289</v>
+        <v>471</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>42</v>
@@ -6498,16 +6502,16 @@
         <v>43</v>
       </c>
       <c r="J71" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="K71" t="s">
-        <v>35</v>
-      </c>
-      <c r="L71" t="s">
-        <v>291</v>
-      </c>
-      <c r="M71" t="s">
-        <v>292</v>
+        <v>220</v>
+      </c>
+      <c r="L71">
+        <v>2100453784</v>
+      </c>
+      <c r="M71">
+        <v>24201579</v>
       </c>
       <c r="P71" t="s">
         <v>38</v>
@@ -6516,48 +6520,48 @@
         <v>38</v>
       </c>
       <c r="T71" t="s">
+        <v>38</v>
+      </c>
+      <c r="U71" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B72">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>203</v>
-      </c>
-      <c r="E72" t="s">
-        <v>31</v>
+        <v>196</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>42</v>
       </c>
       <c r="I72" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J72" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="K72" t="s">
-        <v>220</v>
-      </c>
-      <c r="L72">
-        <v>2100453753</v>
-      </c>
-      <c r="M72">
-        <v>24201551</v>
+        <v>35</v>
+      </c>
+      <c r="L72" t="s">
+        <v>291</v>
+      </c>
+      <c r="M72" t="s">
+        <v>292</v>
       </c>
       <c r="P72" t="s">
         <v>38</v>
@@ -6566,48 +6570,48 @@
         <v>38</v>
       </c>
       <c r="T72" t="s">
-        <v>38</v>
-      </c>
-      <c r="U72" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B73">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D73" t="s">
-        <v>196</v>
+        <v>203</v>
+      </c>
+      <c r="E73" t="s">
+        <v>31</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>532</v>
+        <v>293</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>533</v>
+        <v>294</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>42</v>
       </c>
       <c r="I73" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J73" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K73" t="s">
         <v>220</v>
       </c>
       <c r="L73">
-        <v>2100982067</v>
+        <v>2100453753</v>
       </c>
       <c r="M73">
-        <v>24216836</v>
+        <v>24201551</v>
       </c>
       <c r="P73" t="s">
         <v>38</v>
@@ -6616,15 +6620,18 @@
         <v>38</v>
       </c>
       <c r="T73" t="s">
+        <v>38</v>
+      </c>
+      <c r="U73" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B74">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C74">
         <v>3</v>
@@ -6633,10 +6640,10 @@
         <v>196</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>297</v>
+        <v>532</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>298</v>
+        <v>533</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>42</v>
@@ -6645,16 +6652,16 @@
         <v>43</v>
       </c>
       <c r="J74" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K74" t="s">
-        <v>35</v>
-      </c>
-      <c r="L74" t="s">
-        <v>300</v>
-      </c>
-      <c r="M74" t="s">
-        <v>301</v>
+        <v>220</v>
+      </c>
+      <c r="L74">
+        <v>2100982067</v>
+      </c>
+      <c r="M74">
+        <v>24216836</v>
       </c>
       <c r="P74" t="s">
         <v>38</v>
@@ -6668,43 +6675,40 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B75">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>534</v>
+        <v>297</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>535</v>
+        <v>298</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="I75" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="J75" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="K75" t="s">
         <v>35</v>
       </c>
       <c r="L75" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="M75" t="s">
-        <v>304</v>
-      </c>
-      <c r="N75" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="P75" t="s">
         <v>38</v>
@@ -6712,16 +6716,16 @@
       <c r="Q75" t="s">
         <v>38</v>
       </c>
-      <c r="R75" t="s">
+      <c r="T75" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B76">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -6730,28 +6734,31 @@
         <v>203</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>306</v>
+        <v>534</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>307</v>
+        <v>535</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="I76" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="J76" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="K76" t="s">
-        <v>220</v>
-      </c>
-      <c r="L76">
-        <v>2100453805</v>
-      </c>
-      <c r="M76">
-        <v>24201575</v>
+        <v>35</v>
+      </c>
+      <c r="L76" t="s">
+        <v>303</v>
+      </c>
+      <c r="M76" t="s">
+        <v>304</v>
+      </c>
+      <c r="N76" t="s">
+        <v>305</v>
       </c>
       <c r="P76" t="s">
         <v>38</v>
@@ -6759,52 +6766,46 @@
       <c r="Q76" t="s">
         <v>38</v>
       </c>
-      <c r="T76" t="s">
-        <v>38</v>
-      </c>
-      <c r="U76" t="s">
+      <c r="R76" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B77">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>536</v>
+        <v>306</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>537</v>
+        <v>307</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>235</v>
+        <v>42</v>
       </c>
       <c r="I77" t="s">
-        <v>236</v>
+        <v>47</v>
       </c>
       <c r="J77" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K77" t="s">
         <v>220</v>
       </c>
       <c r="L77">
-        <v>2100453800</v>
+        <v>2100453805</v>
       </c>
       <c r="M77">
-        <v>24201571</v>
-      </c>
-      <c r="O77" t="s">
-        <v>38</v>
+        <v>24201575</v>
       </c>
       <c r="P77" t="s">
         <v>38</v>
@@ -6812,13 +6813,19 @@
       <c r="Q77" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="78" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="T77" t="s">
+        <v>38</v>
+      </c>
+      <c r="U77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B78">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="C78">
         <v>3</v>
@@ -6827,25 +6834,31 @@
         <v>196</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>235</v>
       </c>
+      <c r="I78" t="s">
+        <v>236</v>
+      </c>
       <c r="J78" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K78" t="s">
         <v>220</v>
       </c>
       <c r="L78">
-        <v>2100962292</v>
+        <v>2100453800</v>
       </c>
       <c r="M78">
-        <v>24215956</v>
+        <v>24201571</v>
+      </c>
+      <c r="O78" t="s">
+        <v>38</v>
       </c>
       <c r="P78" t="s">
         <v>38</v>
@@ -6854,144 +6867,138 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B79">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C79">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>311</v>
+        <v>538</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>312</v>
+        <v>539</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="I79" t="s">
-        <v>47</v>
+        <v>235</v>
       </c>
       <c r="J79" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="K79" t="s">
         <v>220</v>
       </c>
       <c r="L79">
-        <v>2100453796</v>
+        <v>2100962292</v>
       </c>
       <c r="M79">
-        <v>24201583</v>
-      </c>
-      <c r="S79" t="s">
+        <v>24215956</v>
+      </c>
+      <c r="P79" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q79" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B80">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D80" t="s">
         <v>203</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>63</v>
+        <v>311</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>475</v>
+        <v>312</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>64</v>
+        <v>469</v>
       </c>
       <c r="I80" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="J80" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K80" t="s">
         <v>220</v>
       </c>
       <c r="L80">
-        <v>2100453772</v>
+        <v>2100453796</v>
       </c>
       <c r="M80">
-        <v>24201559</v>
-      </c>
-      <c r="P80" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q80" t="s">
+        <v>24201583</v>
+      </c>
+      <c r="S80" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B81">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="C81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>540</v>
+        <v>63</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>541</v>
+        <v>475</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>469</v>
+        <v>64</v>
       </c>
       <c r="I81" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="J81" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K81" t="s">
-        <v>35</v>
-      </c>
-      <c r="L81" t="s">
-        <v>316</v>
-      </c>
-      <c r="M81" t="s">
-        <v>317</v>
+        <v>220</v>
+      </c>
+      <c r="L81">
+        <v>2100453772</v>
+      </c>
+      <c r="M81">
+        <v>24201559</v>
       </c>
       <c r="P81" t="s">
         <v>38</v>
       </c>
       <c r="Q81" t="s">
-        <v>38</v>
-      </c>
-      <c r="S81" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B82">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="C82">
         <v>3</v>
@@ -6999,32 +7006,29 @@
       <c r="D82" t="s">
         <v>196</v>
       </c>
-      <c r="E82" t="s">
-        <v>31</v>
-      </c>
       <c r="F82" s="4" t="s">
-        <v>470</v>
+        <v>540</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>471</v>
+        <v>541</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>42</v>
+        <v>469</v>
       </c>
       <c r="I82" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J82" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="K82" t="s">
         <v>35</v>
       </c>
       <c r="L82" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="M82" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="P82" t="s">
         <v>38</v>
@@ -7032,19 +7036,16 @@
       <c r="Q82" t="s">
         <v>38</v>
       </c>
-      <c r="T82" t="s">
-        <v>38</v>
-      </c>
-      <c r="U82" t="s">
+      <c r="S82" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B83">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C83">
         <v>3</v>
@@ -7068,16 +7069,16 @@
         <v>43</v>
       </c>
       <c r="J83" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="K83" t="s">
         <v>35</v>
       </c>
       <c r="L83" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="M83" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="P83" t="s">
         <v>38</v>
@@ -7094,22 +7095,25 @@
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B84">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D84" t="s">
-        <v>203</v>
+        <v>196</v>
+      </c>
+      <c r="E84" t="s">
+        <v>31</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>542</v>
+        <v>470</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>543</v>
+        <v>471</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>42</v>
@@ -7118,16 +7122,16 @@
         <v>43</v>
       </c>
       <c r="J84" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="K84" t="s">
         <v>35</v>
       </c>
       <c r="L84" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="M84" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="P84" t="s">
         <v>38</v>
@@ -7136,48 +7140,48 @@
         <v>38</v>
       </c>
       <c r="T84" t="s">
+        <v>38</v>
+      </c>
+      <c r="U84" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B85">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="C85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>32</v>
+        <v>542</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>465</v>
+        <v>543</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>466</v>
+        <v>42</v>
       </c>
       <c r="I85" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J85" t="s">
-        <v>284</v>
+        <v>324</v>
       </c>
       <c r="K85" t="s">
         <v>35</v>
       </c>
       <c r="L85" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M85" t="s">
-        <v>328</v>
-      </c>
-      <c r="N85" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="P85" t="s">
         <v>38</v>
@@ -7186,18 +7190,15 @@
         <v>38</v>
       </c>
       <c r="T85" t="s">
-        <v>38</v>
-      </c>
-      <c r="V85" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B86">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C86">
         <v>3</v>
@@ -7218,19 +7219,19 @@
         <v>33</v>
       </c>
       <c r="J86" t="s">
-        <v>330</v>
+        <v>284</v>
       </c>
       <c r="K86" t="s">
         <v>35</v>
       </c>
       <c r="L86" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="M86" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="N86" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="P86" t="s">
         <v>38</v>
@@ -7247,10 +7248,10 @@
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B87">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C87">
         <v>3</v>
@@ -7271,19 +7272,19 @@
         <v>33</v>
       </c>
       <c r="J87" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="K87" t="s">
         <v>35</v>
       </c>
       <c r="L87" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="M87" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="N87" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="P87" t="s">
         <v>38</v>
@@ -7300,10 +7301,10 @@
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B88">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C88">
         <v>3</v>
@@ -7312,42 +7313,51 @@
         <v>196</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>338</v>
+        <v>32</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>339</v>
+        <v>465</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>231</v>
+        <v>466</v>
       </c>
       <c r="I88" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J88" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="K88" t="s">
         <v>35</v>
       </c>
       <c r="L88" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="M88" t="s">
-        <v>342</v>
+        <v>336</v>
+      </c>
+      <c r="N88" t="s">
+        <v>337</v>
       </c>
       <c r="P88" t="s">
         <v>38</v>
       </c>
       <c r="Q88" t="s">
+        <v>38</v>
+      </c>
+      <c r="T88" t="s">
+        <v>38</v>
+      </c>
+      <c r="V88" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B89">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C89">
         <v>3</v>
@@ -7356,28 +7366,28 @@
         <v>196</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>40</v>
+        <v>338</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>41</v>
+        <v>339</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>42</v>
+        <v>231</v>
       </c>
       <c r="I89" t="s">
         <v>43</v>
       </c>
       <c r="J89" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="K89" t="s">
-        <v>220</v>
-      </c>
-      <c r="L89">
-        <v>2100453776</v>
-      </c>
-      <c r="M89">
-        <v>24201567</v>
+        <v>35</v>
+      </c>
+      <c r="L89" t="s">
+        <v>341</v>
+      </c>
+      <c r="M89" t="s">
+        <v>342</v>
       </c>
       <c r="P89" t="s">
         <v>38</v>
@@ -7388,10 +7398,10 @@
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B90">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C90">
         <v>3</v>
@@ -7400,10 +7410,10 @@
         <v>196</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>344</v>
+        <v>40</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>345</v>
+        <v>41</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>42</v>
@@ -7412,33 +7422,30 @@
         <v>43</v>
       </c>
       <c r="J90" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="K90" t="s">
-        <v>35</v>
-      </c>
-      <c r="L90" t="s">
-        <v>347</v>
-      </c>
-      <c r="M90" t="s">
-        <v>348</v>
+        <v>220</v>
+      </c>
+      <c r="L90">
+        <v>2100453776</v>
+      </c>
+      <c r="M90">
+        <v>24201567</v>
       </c>
       <c r="P90" t="s">
         <v>38</v>
       </c>
       <c r="Q90" t="s">
-        <v>38</v>
-      </c>
-      <c r="T90" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B91">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C91">
         <v>3</v>
@@ -7447,31 +7454,28 @@
         <v>196</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>32</v>
+        <v>344</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>465</v>
+        <v>345</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>466</v>
+        <v>42</v>
       </c>
       <c r="I91" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J91" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="K91" t="s">
         <v>35</v>
       </c>
       <c r="L91" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="M91" t="s">
-        <v>351</v>
-      </c>
-      <c r="N91" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="P91" t="s">
         <v>38</v>
@@ -7482,16 +7486,13 @@
       <c r="T91" t="s">
         <v>38</v>
       </c>
-      <c r="V91" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="92" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B92">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C92">
         <v>3</v>
@@ -7500,54 +7501,63 @@
         <v>196</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>544</v>
+        <v>32</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>545</v>
+        <v>465</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>71</v>
+        <v>466</v>
       </c>
       <c r="I92" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="J92" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="K92" t="s">
         <v>35</v>
       </c>
       <c r="L92" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="M92" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="N92" t="s">
-        <v>356</v>
+        <v>352</v>
+      </c>
+      <c r="P92" t="s">
+        <v>38</v>
       </c>
       <c r="Q92" t="s">
+        <v>38</v>
+      </c>
+      <c r="T92" t="s">
+        <v>38</v>
+      </c>
+      <c r="V92" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B93">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>488</v>
+        <v>544</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>489</v>
+        <v>545</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>71</v>
@@ -7556,77 +7566,77 @@
         <v>72</v>
       </c>
       <c r="J93" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="K93" t="s">
-        <v>220</v>
-      </c>
-      <c r="L93">
-        <v>2100513261</v>
-      </c>
-      <c r="M93">
-        <v>24202242</v>
-      </c>
-      <c r="P93" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="L93" t="s">
+        <v>354</v>
+      </c>
+      <c r="M93" t="s">
+        <v>355</v>
+      </c>
+      <c r="N93" t="s">
+        <v>356</v>
       </c>
       <c r="Q93" t="s">
-        <v>38</v>
-      </c>
-      <c r="R93" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="94" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B94">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D94" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>358</v>
+        <v>488</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>359</v>
+        <v>489</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>546</v>
+        <v>71</v>
       </c>
       <c r="I94" t="s">
-        <v>360</v>
+        <v>72</v>
       </c>
       <c r="J94" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="K94" t="s">
         <v>220</v>
       </c>
       <c r="L94">
-        <v>2100962313</v>
+        <v>2100513261</v>
       </c>
       <c r="M94">
-        <v>24215955</v>
+        <v>24202242</v>
       </c>
       <c r="P94" t="s">
         <v>38</v>
       </c>
       <c r="Q94" t="s">
+        <v>38</v>
+      </c>
+      <c r="R94" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B95">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C95">
         <v>3</v>
@@ -7635,31 +7645,28 @@
         <v>196</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>235</v>
+        <v>546</v>
       </c>
       <c r="I95" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J95" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K95" t="s">
         <v>220</v>
       </c>
       <c r="L95">
-        <v>2100513264</v>
+        <v>2100962313</v>
       </c>
       <c r="M95">
-        <v>24202245</v>
-      </c>
-      <c r="O95" t="s">
-        <v>38</v>
+        <v>24215955</v>
       </c>
       <c r="P95" t="s">
         <v>38</v>
@@ -7668,12 +7675,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B96">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C96">
         <v>3</v>
@@ -7682,10 +7689,10 @@
         <v>196</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>547</v>
+        <v>362</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>548</v>
+        <v>363</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>235</v>
@@ -7694,16 +7701,19 @@
         <v>364</v>
       </c>
       <c r="J96" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K96" t="s">
         <v>220</v>
       </c>
       <c r="L96">
-        <v>2100513266</v>
+        <v>2100513264</v>
       </c>
       <c r="M96">
-        <v>24202247</v>
+        <v>24202245</v>
+      </c>
+      <c r="O96" t="s">
+        <v>38</v>
       </c>
       <c r="P96" t="s">
         <v>38</v>
@@ -7712,42 +7722,42 @@
         <v>38</v>
       </c>
     </row>
-    <row r="97" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B97">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C97">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>71</v>
+        <v>235</v>
       </c>
       <c r="I97" t="s">
-        <v>72</v>
+        <v>364</v>
       </c>
       <c r="J97" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K97" t="s">
         <v>220</v>
       </c>
       <c r="L97">
-        <v>2100513265</v>
+        <v>2100513266</v>
       </c>
       <c r="M97">
-        <v>24202246</v>
+        <v>24202247</v>
       </c>
       <c r="P97" t="s">
         <v>38</v>
@@ -7756,24 +7766,24 @@
         <v>38</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B98">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C98">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D98" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>368</v>
+        <v>549</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>369</v>
+        <v>550</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>71</v>
@@ -7782,100 +7792,100 @@
         <v>72</v>
       </c>
       <c r="J98" t="s">
+        <v>367</v>
+      </c>
+      <c r="K98" t="s">
+        <v>220</v>
+      </c>
+      <c r="L98">
+        <v>2100513265</v>
+      </c>
+      <c r="M98">
+        <v>24202246</v>
+      </c>
+      <c r="P98" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>94</v>
+      </c>
+      <c r="B99">
+        <v>1274</v>
+      </c>
+      <c r="C99">
+        <v>9</v>
+      </c>
+      <c r="D99" t="s">
+        <v>196</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I99" t="s">
+        <v>72</v>
+      </c>
+      <c r="J99" t="s">
         <v>370</v>
       </c>
-      <c r="K98" t="s">
+      <c r="K99" t="s">
         <v>35</v>
       </c>
-      <c r="L98" t="s">
+      <c r="L99" t="s">
         <v>371</v>
       </c>
-      <c r="M98" t="s">
+      <c r="M99" t="s">
         <v>372</v>
       </c>
-      <c r="N98" t="s">
+      <c r="N99" t="s">
         <v>373</v>
       </c>
-      <c r="P98" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B99">
+      <c r="P99" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B100">
         <v>1275</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D100" t="s">
         <v>374</v>
       </c>
-      <c r="F99" s="13" t="s">
+      <c r="F100" s="13" t="s">
         <v>551</v>
       </c>
-      <c r="G99" s="10" t="s">
+      <c r="G100" s="10" t="s">
         <v>552</v>
       </c>
-      <c r="H99" s="14" t="s">
+      <c r="H100" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="P99" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q99" t="s">
-        <v>38</v>
-      </c>
-      <c r="T99" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>95</v>
-      </c>
-      <c r="B100">
-        <v>1276</v>
-      </c>
-      <c r="C100">
-        <v>1</v>
-      </c>
-      <c r="D100" t="s">
-        <v>203</v>
-      </c>
-      <c r="E100" t="s">
-        <v>375</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>554</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I100" t="s">
-        <v>72</v>
-      </c>
-      <c r="J100" t="s">
-        <v>376</v>
-      </c>
-      <c r="K100" t="s">
-        <v>377</v>
-      </c>
-      <c r="L100">
-        <v>2101340855</v>
-      </c>
-      <c r="M100">
-        <v>24224306</v>
+      <c r="P100" t="s">
+        <v>38</v>
       </c>
       <c r="Q100" t="s">
+        <v>38</v>
+      </c>
+      <c r="T100" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B101">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -7883,11 +7893,14 @@
       <c r="D101" t="s">
         <v>203</v>
       </c>
+      <c r="E101" t="s">
+        <v>375</v>
+      </c>
       <c r="F101" s="4" t="s">
-        <v>378</v>
+        <v>553</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>71</v>
@@ -7896,36 +7909,27 @@
         <v>72</v>
       </c>
       <c r="J101" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="K101" t="s">
-        <v>35</v>
-      </c>
-      <c r="L101" t="s">
-        <v>380</v>
-      </c>
-      <c r="M101" t="s">
-        <v>381</v>
-      </c>
-      <c r="N101" t="s">
-        <v>382</v>
-      </c>
-      <c r="P101" t="s">
-        <v>38</v>
+        <v>377</v>
+      </c>
+      <c r="L101">
+        <v>2101340855</v>
+      </c>
+      <c r="M101">
+        <v>24224306</v>
       </c>
       <c r="Q101" t="s">
-        <v>38</v>
-      </c>
-      <c r="R101" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B102">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -7946,16 +7950,16 @@
         <v>72</v>
       </c>
       <c r="J102" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="K102" t="s">
         <v>35</v>
       </c>
       <c r="L102" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="M102" t="s">
-        <v>239</v>
+        <v>381</v>
       </c>
       <c r="N102" t="s">
         <v>382</v>
@@ -7970,12 +7974,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="103" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B103">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -7983,14 +7987,11 @@
       <c r="D103" t="s">
         <v>203</v>
       </c>
-      <c r="E103" t="s">
-        <v>375</v>
-      </c>
       <c r="F103" s="4" t="s">
-        <v>556</v>
+        <v>378</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>71</v>
@@ -7999,27 +8000,36 @@
         <v>72</v>
       </c>
       <c r="J103" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="K103" t="s">
-        <v>377</v>
-      </c>
-      <c r="L103">
-        <v>2101340843</v>
-      </c>
-      <c r="M103">
-        <v>24224300</v>
+        <v>35</v>
+      </c>
+      <c r="L103" t="s">
+        <v>384</v>
+      </c>
+      <c r="M103" t="s">
+        <v>239</v>
+      </c>
+      <c r="N103" t="s">
+        <v>382</v>
+      </c>
+      <c r="P103" t="s">
+        <v>38</v>
       </c>
       <c r="Q103" t="s">
+        <v>38</v>
+      </c>
+      <c r="R103" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="104" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B104">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -8031,10 +8041,10 @@
         <v>375</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>71</v>
@@ -8043,27 +8053,27 @@
         <v>72</v>
       </c>
       <c r="J104" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K104" t="s">
         <v>377</v>
       </c>
       <c r="L104">
-        <v>2101340847</v>
+        <v>2101340843</v>
       </c>
       <c r="M104">
-        <v>24224302</v>
+        <v>24224300</v>
       </c>
       <c r="Q104" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B105">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -8075,10 +8085,10 @@
         <v>375</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>71</v>
@@ -8087,27 +8097,27 @@
         <v>72</v>
       </c>
       <c r="J105" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K105" t="s">
         <v>377</v>
       </c>
       <c r="L105">
-        <v>2101340852</v>
+        <v>2101340847</v>
       </c>
       <c r="M105">
-        <v>24224305</v>
+        <v>24224302</v>
       </c>
       <c r="Q105" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B106">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -8119,10 +8129,10 @@
         <v>375</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>71</v>
@@ -8131,16 +8141,16 @@
         <v>72</v>
       </c>
       <c r="J106" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K106" t="s">
         <v>377</v>
       </c>
       <c r="L106">
-        <v>2101340842</v>
+        <v>2101340852</v>
       </c>
       <c r="M106">
-        <v>24224299</v>
+        <v>24224305</v>
       </c>
       <c r="Q106" t="s">
         <v>38</v>
@@ -8148,10 +8158,10 @@
     </row>
     <row r="107" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B107">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C107">
         <v>1</v>
@@ -8175,27 +8185,27 @@
         <v>72</v>
       </c>
       <c r="J107" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K107" t="s">
         <v>377</v>
       </c>
       <c r="L107">
-        <v>2101340850</v>
+        <v>2101340842</v>
       </c>
       <c r="M107">
-        <v>24224304</v>
+        <v>24224299</v>
       </c>
       <c r="Q107" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B108">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -8207,10 +8217,10 @@
         <v>375</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H108" s="3" t="s">
         <v>71</v>
@@ -8219,16 +8229,16 @@
         <v>72</v>
       </c>
       <c r="J108" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K108" t="s">
         <v>377</v>
       </c>
       <c r="L108">
-        <v>2101340839</v>
+        <v>2101340850</v>
       </c>
       <c r="M108">
-        <v>24224297</v>
+        <v>24224304</v>
       </c>
       <c r="Q108" t="s">
         <v>38</v>
@@ -8236,10 +8246,10 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B109">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C109">
         <v>1</v>
@@ -8251,10 +8261,10 @@
         <v>375</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>71</v>
@@ -8263,16 +8273,16 @@
         <v>72</v>
       </c>
       <c r="J109" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K109" t="s">
         <v>377</v>
       </c>
       <c r="L109">
-        <v>2101340840</v>
+        <v>2101340839</v>
       </c>
       <c r="M109">
-        <v>24224298</v>
+        <v>24224297</v>
       </c>
       <c r="Q109" t="s">
         <v>38</v>
@@ -8280,104 +8290,107 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B110">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D110" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="E110" t="s">
-        <v>31</v>
-      </c>
-      <c r="F110" s="9" t="s">
-        <v>470</v>
+        <v>375</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>566</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>471</v>
+        <v>567</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="I110" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="J110" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K110" t="s">
-        <v>35</v>
-      </c>
-      <c r="L110" t="s">
-        <v>393</v>
-      </c>
-      <c r="M110" t="s">
-        <v>394</v>
-      </c>
-      <c r="P110" t="s">
-        <v>38</v>
+        <v>377</v>
+      </c>
+      <c r="L110">
+        <v>2101340840</v>
+      </c>
+      <c r="M110">
+        <v>24224298</v>
       </c>
       <c r="Q110" t="s">
-        <v>38</v>
-      </c>
-      <c r="T110" t="s">
-        <v>38</v>
-      </c>
-      <c r="U110" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B111">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C111">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D111" t="s">
         <v>196</v>
       </c>
-      <c r="F111" s="4" t="s">
-        <v>568</v>
+      <c r="E111" t="s">
+        <v>31</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>470</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>395</v>
+        <v>471</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="I111" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="J111" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="K111" t="s">
-        <v>220</v>
-      </c>
-      <c r="L111">
-        <v>2100779050</v>
-      </c>
-      <c r="M111">
-        <v>29269571</v>
+        <v>35</v>
+      </c>
+      <c r="L111" t="s">
+        <v>393</v>
+      </c>
+      <c r="M111" t="s">
+        <v>394</v>
+      </c>
+      <c r="P111" t="s">
+        <v>38</v>
       </c>
       <c r="Q111" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="112" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="T111" t="s">
+        <v>38</v>
+      </c>
+      <c r="U111" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B112">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C112">
         <v>9</v>
@@ -8386,10 +8399,10 @@
         <v>196</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>71</v>
@@ -8398,27 +8411,27 @@
         <v>72</v>
       </c>
       <c r="J112" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K112" t="s">
         <v>220</v>
       </c>
       <c r="L112">
-        <v>2100779043</v>
+        <v>2100779050</v>
       </c>
       <c r="M112">
-        <v>29282287</v>
+        <v>29269571</v>
       </c>
       <c r="Q112" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B113">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C113">
         <v>9</v>
@@ -8427,10 +8440,10 @@
         <v>196</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>399</v>
+        <v>569</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>71</v>
@@ -8439,16 +8452,16 @@
         <v>72</v>
       </c>
       <c r="J113" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="K113" t="s">
         <v>220</v>
       </c>
       <c r="L113">
-        <v>2100453763</v>
+        <v>2100779043</v>
       </c>
       <c r="M113">
-        <v>24201546</v>
+        <v>29282287</v>
       </c>
       <c r="Q113" t="s">
         <v>38</v>
@@ -8456,40 +8469,40 @@
     </row>
     <row r="114" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B114">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C114">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D114" t="s">
         <v>196</v>
       </c>
-      <c r="E114" t="s">
-        <v>31</v>
-      </c>
       <c r="F114" s="4" t="s">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="I114" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="J114" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="K114" t="s">
         <v>220</v>
       </c>
-      <c r="P114" t="s">
-        <v>38</v>
+      <c r="L114">
+        <v>2100453763</v>
+      </c>
+      <c r="M114">
+        <v>24201546</v>
       </c>
       <c r="Q114" t="s">
         <v>38</v>
@@ -8497,10 +8510,10 @@
     </row>
     <row r="115" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B115">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="C115">
         <v>3</v>
@@ -8512,29 +8525,23 @@
         <v>31</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>570</v>
+        <v>59</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>571</v>
+        <v>402</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="I115" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="J115" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K115" t="s">
         <v>220</v>
       </c>
-      <c r="L115">
-        <v>2100453822</v>
-      </c>
-      <c r="M115">
-        <v>24201569</v>
-      </c>
       <c r="P115" t="s">
         <v>38</v>
       </c>
@@ -8544,10 +8551,10 @@
     </row>
     <row r="116" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B116">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="C116">
         <v>3</v>
@@ -8559,10 +8566,10 @@
         <v>31</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>71</v>
@@ -8571,16 +8578,16 @@
         <v>72</v>
       </c>
       <c r="J116" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K116" t="s">
         <v>220</v>
       </c>
       <c r="L116">
-        <v>2100894168</v>
+        <v>2100453822</v>
       </c>
       <c r="M116">
-        <v>24210519</v>
+        <v>24201569</v>
       </c>
       <c r="P116" t="s">
         <v>38</v>
@@ -8591,10 +8598,10 @@
     </row>
     <row r="117" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B117">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="C117">
         <v>3</v>
@@ -8606,10 +8613,10 @@
         <v>31</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>406</v>
+        <v>572</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>88</v>
+        <v>573</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>71</v>
@@ -8618,19 +8625,16 @@
         <v>72</v>
       </c>
       <c r="J117" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="K117" t="s">
-        <v>35</v>
-      </c>
-      <c r="L117" t="s">
-        <v>408</v>
-      </c>
-      <c r="M117" t="s">
-        <v>409</v>
-      </c>
-      <c r="N117" t="s">
-        <v>410</v>
+        <v>220</v>
+      </c>
+      <c r="L117">
+        <v>2100894168</v>
+      </c>
+      <c r="M117">
+        <v>24210519</v>
       </c>
       <c r="P117" t="s">
         <v>38</v>
@@ -8641,10 +8645,10 @@
     </row>
     <row r="118" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B118">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C118">
         <v>3</v>
@@ -8656,28 +8660,31 @@
         <v>31</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>412</v>
+        <v>88</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I118" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="J118" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="K118" t="s">
         <v>35</v>
       </c>
       <c r="L118" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="M118" t="s">
-        <v>415</v>
+        <v>409</v>
+      </c>
+      <c r="N118" t="s">
+        <v>410</v>
       </c>
       <c r="P118" t="s">
         <v>38</v>
@@ -8688,10 +8695,10 @@
     </row>
     <row r="119" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B119">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C119">
         <v>3</v>
@@ -8703,45 +8710,42 @@
         <v>31</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>574</v>
+        <v>411</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>575</v>
+        <v>412</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="I119" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J119" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="K119" t="s">
-        <v>220</v>
-      </c>
-      <c r="L119">
-        <v>2100453774</v>
-      </c>
-      <c r="M119">
-        <v>24201562</v>
+        <v>35</v>
+      </c>
+      <c r="L119" t="s">
+        <v>414</v>
+      </c>
+      <c r="M119" t="s">
+        <v>415</v>
       </c>
       <c r="P119" t="s">
         <v>38</v>
       </c>
       <c r="Q119" t="s">
-        <v>38</v>
-      </c>
-      <c r="T119" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="120" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B120">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C120">
         <v>3</v>
@@ -8753,10 +8757,10 @@
         <v>31</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>470</v>
+        <v>574</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>471</v>
+        <v>575</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>42</v>
@@ -8765,16 +8769,16 @@
         <v>43</v>
       </c>
       <c r="J120" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="K120" t="s">
-        <v>35</v>
-      </c>
-      <c r="L120" t="s">
-        <v>418</v>
-      </c>
-      <c r="M120" t="s">
-        <v>394</v>
+        <v>220</v>
+      </c>
+      <c r="L120">
+        <v>2100453774</v>
+      </c>
+      <c r="M120">
+        <v>24201562</v>
       </c>
       <c r="P120" t="s">
         <v>38</v>
@@ -8783,18 +8787,15 @@
         <v>38</v>
       </c>
       <c r="T120" t="s">
-        <v>38</v>
-      </c>
-      <c r="U120" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="121" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B121">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="C121">
         <v>3</v>
@@ -8818,16 +8819,16 @@
         <v>43</v>
       </c>
       <c r="J121" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="K121" t="s">
         <v>35</v>
       </c>
       <c r="L121" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="M121" t="s">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="P121" t="s">
         <v>38</v>
@@ -8844,10 +8845,10 @@
     </row>
     <row r="122" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B122">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="C122">
         <v>3</v>
@@ -8859,45 +8860,48 @@
         <v>31</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>59</v>
+        <v>470</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>402</v>
+        <v>471</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="I122" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="J122" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K122" t="s">
         <v>35</v>
       </c>
       <c r="L122" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="M122" t="s">
-        <v>424</v>
-      </c>
-      <c r="N122" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="P122" t="s">
         <v>38</v>
       </c>
       <c r="Q122" t="s">
+        <v>38</v>
+      </c>
+      <c r="T122" t="s">
+        <v>38</v>
+      </c>
+      <c r="U122" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="123" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B123">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C123">
         <v>3</v>
@@ -8909,107 +8913,101 @@
         <v>31</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>465</v>
+        <v>402</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>466</v>
+        <v>54</v>
       </c>
       <c r="I123" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="J123" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="K123" t="s">
         <v>35</v>
       </c>
       <c r="L123" t="s">
+        <v>423</v>
+      </c>
+      <c r="M123" t="s">
+        <v>424</v>
+      </c>
+      <c r="N123" t="s">
+        <v>425</v>
+      </c>
+      <c r="P123" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="124" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>118</v>
+      </c>
+      <c r="B124">
+        <v>1299</v>
+      </c>
+      <c r="C124">
+        <v>3</v>
+      </c>
+      <c r="D124" t="s">
+        <v>196</v>
+      </c>
+      <c r="E124" t="s">
+        <v>31</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="I124" t="s">
+        <v>33</v>
+      </c>
+      <c r="J124" t="s">
+        <v>416</v>
+      </c>
+      <c r="K124" t="s">
+        <v>35</v>
+      </c>
+      <c r="L124" t="s">
         <v>426</v>
       </c>
-      <c r="M123" t="s">
+      <c r="M124" t="s">
         <v>427</v>
       </c>
-      <c r="N123" t="s">
+      <c r="N124" t="s">
         <v>337</v>
       </c>
-      <c r="P123" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q123" t="s">
-        <v>38</v>
-      </c>
-      <c r="T123" t="s">
-        <v>38</v>
-      </c>
-      <c r="V123" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="124" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A124">
-        <v>119</v>
-      </c>
-      <c r="B124">
-        <v>1381</v>
-      </c>
-      <c r="C124">
-        <v>7</v>
-      </c>
-      <c r="D124" t="s">
-        <v>30</v>
-      </c>
-      <c r="E124" t="s">
-        <v>15</v>
-      </c>
-      <c r="F124" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="G124" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I124" t="s">
-        <v>72</v>
-      </c>
-      <c r="J124" t="s">
-        <v>428</v>
-      </c>
-      <c r="K124" t="s">
-        <v>429</v>
-      </c>
-      <c r="L124">
-        <v>684495</v>
-      </c>
-      <c r="M124">
-        <v>60208578</v>
-      </c>
-      <c r="O124" t="s">
-        <v>38</v>
-      </c>
       <c r="P124" t="s">
         <v>38</v>
       </c>
       <c r="Q124" t="s">
         <v>38</v>
       </c>
-      <c r="S124" t="s">
-        <v>38</v>
-      </c>
       <c r="T124" t="s">
+        <v>38</v>
+      </c>
+      <c r="V124" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="125" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B125">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C125">
         <v>7</v>
@@ -9021,19 +9019,19 @@
         <v>15</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>430</v>
+        <v>576</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>431</v>
+        <v>577</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>469</v>
+        <v>71</v>
       </c>
       <c r="I125" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="J125" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="K125" t="s">
         <v>429</v>
@@ -9041,6 +9039,9 @@
       <c r="L125">
         <v>684495</v>
       </c>
+      <c r="M125">
+        <v>60208578</v>
+      </c>
       <c r="O125" t="s">
         <v>38</v>
       </c>
@@ -9056,16 +9057,13 @@
       <c r="T125" t="s">
         <v>38</v>
       </c>
-      <c r="U125" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B126">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="C126">
         <v>7</v>
@@ -9077,19 +9075,19 @@
         <v>15</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>297</v>
+        <v>430</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>298</v>
+        <v>431</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>42</v>
+        <v>469</v>
       </c>
       <c r="I126" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J126" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K126" t="s">
         <v>429</v>
@@ -9118,10 +9116,10 @@
     </row>
     <row r="127" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B127">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="C127">
         <v>7</v>
@@ -9133,19 +9131,19 @@
         <v>15</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>578</v>
+        <v>297</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>434</v>
+        <v>298</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="I127" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J127" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K127" t="s">
         <v>429</v>
@@ -9153,9 +9151,6 @@
       <c r="L127">
         <v>684495</v>
       </c>
-      <c r="M127">
-        <v>60208272</v>
-      </c>
       <c r="O127" t="s">
         <v>38</v>
       </c>
@@ -9177,10 +9172,10 @@
     </row>
     <row r="128" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B128">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="C128">
         <v>7</v>
@@ -9192,19 +9187,19 @@
         <v>15</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>436</v>
+        <v>578</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>438</v>
+        <v>64</v>
       </c>
       <c r="I128" t="s">
-        <v>439</v>
+        <v>47</v>
       </c>
       <c r="J128" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="K128" t="s">
         <v>429</v>
@@ -9212,6 +9207,9 @@
       <c r="L128">
         <v>684495</v>
       </c>
+      <c r="M128">
+        <v>60208272</v>
+      </c>
       <c r="O128" t="s">
         <v>38</v>
       </c>
@@ -9227,13 +9225,16 @@
       <c r="T128" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="129" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="U128" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B129">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="C129">
         <v>7</v>
@@ -9245,19 +9246,19 @@
         <v>15</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>549</v>
+        <v>436</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>550</v>
+        <v>437</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>71</v>
+        <v>438</v>
       </c>
       <c r="I129" t="s">
-        <v>72</v>
+        <v>439</v>
       </c>
       <c r="J129" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K129" t="s">
         <v>429</v>
@@ -9265,9 +9266,6 @@
       <c r="L129">
         <v>684495</v>
       </c>
-      <c r="M129">
-        <v>60208270</v>
-      </c>
       <c r="O129" t="s">
         <v>38</v>
       </c>
@@ -9283,16 +9281,13 @@
       <c r="T129" t="s">
         <v>38</v>
       </c>
-      <c r="U129" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B130">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="C130">
         <v>7</v>
@@ -9304,10 +9299,10 @@
         <v>15</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>442</v>
+        <v>549</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>443</v>
+        <v>550</v>
       </c>
       <c r="H130" s="3" t="s">
         <v>71</v>
@@ -9316,7 +9311,7 @@
         <v>72</v>
       </c>
       <c r="J130" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="K130" t="s">
         <v>429</v>
@@ -9325,7 +9320,7 @@
         <v>684495</v>
       </c>
       <c r="M130">
-        <v>60208269</v>
+        <v>60208270</v>
       </c>
       <c r="O130" t="s">
         <v>38</v>
@@ -9334,9 +9329,6 @@
         <v>38</v>
       </c>
       <c r="Q130" t="s">
-        <v>38</v>
-      </c>
-      <c r="R130" t="s">
         <v>38</v>
       </c>
       <c r="S130" t="s">
@@ -9351,10 +9343,10 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B131">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C131">
         <v>7</v>
@@ -9378,7 +9370,7 @@
         <v>72</v>
       </c>
       <c r="J131" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K131" t="s">
         <v>429</v>
@@ -9387,7 +9379,7 @@
         <v>684495</v>
       </c>
       <c r="M131">
-        <v>60208268</v>
+        <v>60208269</v>
       </c>
       <c r="O131" t="s">
         <v>38</v>
@@ -9413,10 +9405,10 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B132">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="C132">
         <v>7</v>
@@ -9428,10 +9420,10 @@
         <v>15</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>517</v>
+        <v>442</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>518</v>
+        <v>443</v>
       </c>
       <c r="H132" s="3" t="s">
         <v>71</v>
@@ -9440,7 +9432,7 @@
         <v>72</v>
       </c>
       <c r="J132" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K132" t="s">
         <v>429</v>
@@ -9449,7 +9441,7 @@
         <v>684495</v>
       </c>
       <c r="M132">
-        <v>60208267</v>
+        <v>60208268</v>
       </c>
       <c r="O132" t="s">
         <v>38</v>
@@ -9458,6 +9450,9 @@
         <v>38</v>
       </c>
       <c r="Q132" t="s">
+        <v>38</v>
+      </c>
+      <c r="R132" t="s">
         <v>38</v>
       </c>
       <c r="S132" t="s">
@@ -9472,10 +9467,10 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B133">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="C133">
         <v>7</v>
@@ -9487,10 +9482,10 @@
         <v>15</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>256</v>
+        <v>517</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>257</v>
+        <v>518</v>
       </c>
       <c r="H133" s="3" t="s">
         <v>71</v>
@@ -9499,7 +9494,7 @@
         <v>72</v>
       </c>
       <c r="J133" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="K133" t="s">
         <v>429</v>
@@ -9508,7 +9503,7 @@
         <v>684495</v>
       </c>
       <c r="M133">
-        <v>60208266</v>
+        <v>60208267</v>
       </c>
       <c r="O133" t="s">
         <v>38</v>
@@ -9531,10 +9526,10 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B134">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="C134">
         <v>7</v>
@@ -9546,10 +9541,10 @@
         <v>15</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>572</v>
+        <v>256</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>573</v>
+        <v>257</v>
       </c>
       <c r="H134" s="3" t="s">
         <v>71</v>
@@ -9558,7 +9553,7 @@
         <v>72</v>
       </c>
       <c r="J134" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="K134" t="s">
         <v>429</v>
@@ -9567,7 +9562,7 @@
         <v>684495</v>
       </c>
       <c r="M134">
-        <v>60208265</v>
+        <v>60208266</v>
       </c>
       <c r="O134" t="s">
         <v>38</v>
@@ -9576,9 +9571,6 @@
         <v>38</v>
       </c>
       <c r="Q134" t="s">
-        <v>38</v>
-      </c>
-      <c r="R134" t="s">
         <v>38</v>
       </c>
       <c r="S134" t="s">
@@ -9593,10 +9585,10 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B135">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="C135">
         <v>7</v>
@@ -9608,10 +9600,10 @@
         <v>15</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>449</v>
+        <v>572</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>450</v>
+        <v>573</v>
       </c>
       <c r="H135" s="3" t="s">
         <v>71</v>
@@ -9620,7 +9612,7 @@
         <v>72</v>
       </c>
       <c r="J135" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="K135" t="s">
         <v>429</v>
@@ -9629,7 +9621,7 @@
         <v>684495</v>
       </c>
       <c r="M135">
-        <v>60208264</v>
+        <v>60208265</v>
       </c>
       <c r="O135" t="s">
         <v>38</v>
@@ -9638,6 +9630,9 @@
         <v>38</v>
       </c>
       <c r="Q135" t="s">
+        <v>38</v>
+      </c>
+      <c r="R135" t="s">
         <v>38</v>
       </c>
       <c r="S135" t="s">
@@ -9652,10 +9647,10 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B136">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="C136">
         <v>7</v>
@@ -9667,10 +9662,10 @@
         <v>15</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>399</v>
+        <v>449</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="H136" s="3" t="s">
         <v>71</v>
@@ -9679,7 +9674,7 @@
         <v>72</v>
       </c>
       <c r="J136" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K136" t="s">
         <v>429</v>
@@ -9688,7 +9683,7 @@
         <v>684495</v>
       </c>
       <c r="M136">
-        <v>60208263</v>
+        <v>60208264</v>
       </c>
       <c r="O136" t="s">
         <v>38</v>
@@ -9711,10 +9706,10 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B137">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="C137">
         <v>7</v>
@@ -9726,10 +9721,10 @@
         <v>15</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>555</v>
+        <v>400</v>
       </c>
       <c r="H137" s="3" t="s">
         <v>71</v>
@@ -9738,7 +9733,7 @@
         <v>72</v>
       </c>
       <c r="J137" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K137" t="s">
         <v>429</v>
@@ -9747,7 +9742,7 @@
         <v>684495</v>
       </c>
       <c r="M137">
-        <v>60208262</v>
+        <v>60208263</v>
       </c>
       <c r="O137" t="s">
         <v>38</v>
@@ -9756,9 +9751,6 @@
         <v>38</v>
       </c>
       <c r="Q137" t="s">
-        <v>38</v>
-      </c>
-      <c r="R137" t="s">
         <v>38</v>
       </c>
       <c r="S137" t="s">
@@ -9773,10 +9765,10 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B138">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="C138">
         <v>7</v>
@@ -9788,10 +9780,10 @@
         <v>15</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>579</v>
+        <v>378</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>489</v>
+        <v>555</v>
       </c>
       <c r="H138" s="3" t="s">
         <v>71</v>
@@ -9800,7 +9792,7 @@
         <v>72</v>
       </c>
       <c r="J138" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K138" t="s">
         <v>429</v>
@@ -9809,7 +9801,7 @@
         <v>684495</v>
       </c>
       <c r="M138">
-        <v>60208261</v>
+        <v>60208262</v>
       </c>
       <c r="O138" t="s">
         <v>38</v>
@@ -9829,13 +9821,16 @@
       <c r="T138" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="139" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="U138" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B139">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C139">
         <v>7</v>
@@ -9847,10 +9842,10 @@
         <v>15</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>563</v>
+        <v>489</v>
       </c>
       <c r="H139" s="3" t="s">
         <v>71</v>
@@ -9859,7 +9854,7 @@
         <v>72</v>
       </c>
       <c r="J139" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K139" t="s">
         <v>429</v>
@@ -9868,7 +9863,7 @@
         <v>684495</v>
       </c>
       <c r="M139">
-        <v>60208260</v>
+        <v>60208261</v>
       </c>
       <c r="O139" t="s">
         <v>38</v>
@@ -9879,22 +9874,22 @@
       <c r="Q139" t="s">
         <v>38</v>
       </c>
+      <c r="R139" t="s">
+        <v>38</v>
+      </c>
       <c r="S139" t="s">
         <v>38</v>
       </c>
       <c r="T139" t="s">
-        <v>38</v>
-      </c>
-      <c r="U139" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="140" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B140">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="C140">
         <v>7</v>
@@ -9918,7 +9913,7 @@
         <v>72</v>
       </c>
       <c r="J140" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K140" t="s">
         <v>429</v>
@@ -9927,7 +9922,7 @@
         <v>684495</v>
       </c>
       <c r="M140">
-        <v>60208259</v>
+        <v>60208260</v>
       </c>
       <c r="O140" t="s">
         <v>38</v>
@@ -9950,10 +9945,10 @@
     </row>
     <row r="141" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B141">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="C141">
         <v>7</v>
@@ -9965,10 +9960,10 @@
         <v>15</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>488</v>
+        <v>562</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>489</v>
+        <v>563</v>
       </c>
       <c r="H141" s="3" t="s">
         <v>71</v>
@@ -9977,7 +9972,7 @@
         <v>72</v>
       </c>
       <c r="J141" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K141" t="s">
         <v>429</v>
@@ -9986,7 +9981,7 @@
         <v>684495</v>
       </c>
       <c r="M141">
-        <v>60208258</v>
+        <v>60208259</v>
       </c>
       <c r="O141" t="s">
         <v>38</v>
@@ -10009,10 +10004,10 @@
     </row>
     <row r="142" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B142">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="C142">
         <v>7</v>
@@ -10024,10 +10019,10 @@
         <v>15</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>580</v>
+        <v>488</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>581</v>
+        <v>489</v>
       </c>
       <c r="H142" s="3" t="s">
         <v>71</v>
@@ -10036,7 +10031,7 @@
         <v>72</v>
       </c>
       <c r="J142" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K142" t="s">
         <v>429</v>
@@ -10045,91 +10040,151 @@
         <v>684495</v>
       </c>
       <c r="M142">
+        <v>60208258</v>
+      </c>
+      <c r="O142" t="s">
+        <v>38</v>
+      </c>
+      <c r="P142" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>38</v>
+      </c>
+      <c r="S142" t="s">
+        <v>38</v>
+      </c>
+      <c r="T142" t="s">
+        <v>38</v>
+      </c>
+      <c r="U142" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>137</v>
+      </c>
+      <c r="B143">
+        <v>1399</v>
+      </c>
+      <c r="C143">
+        <v>7</v>
+      </c>
+      <c r="D143" t="s">
+        <v>30</v>
+      </c>
+      <c r="E143" t="s">
+        <v>15</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I143" t="s">
+        <v>72</v>
+      </c>
+      <c r="J143" t="s">
+        <v>458</v>
+      </c>
+      <c r="K143" t="s">
+        <v>429</v>
+      </c>
+      <c r="L143">
+        <v>684495</v>
+      </c>
+      <c r="M143">
         <v>60208257</v>
       </c>
-      <c r="O142" t="s">
-        <v>38</v>
-      </c>
-      <c r="P142" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q142" t="s">
-        <v>38</v>
-      </c>
-      <c r="S142" t="s">
-        <v>38</v>
-      </c>
-      <c r="T142" t="s">
-        <v>38</v>
-      </c>
-      <c r="U142" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="147" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="O147" t="s">
+      <c r="O143" t="s">
+        <v>38</v>
+      </c>
+      <c r="P143" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>38</v>
+      </c>
+      <c r="S143" t="s">
+        <v>38</v>
+      </c>
+      <c r="T143" t="s">
+        <v>38</v>
+      </c>
+      <c r="U143" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="148" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="O148" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="148" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="I148" t="s">
+    <row r="149" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="I149" t="s">
         <v>460</v>
       </c>
-      <c r="J148" t="s">
+      <c r="J149" t="s">
         <v>30</v>
       </c>
-      <c r="K148" t="s">
+      <c r="K149" t="s">
         <v>196</v>
       </c>
-      <c r="L148" t="s">
+      <c r="L149" t="s">
         <v>203</v>
       </c>
-      <c r="O148" t="s">
+      <c r="O149" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="149" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H149" t="s">
+    <row r="150" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H150" t="s">
         <v>35</v>
       </c>
-      <c r="I149">
+      <c r="I150">
         <v>75</v>
       </c>
-      <c r="J149">
+      <c r="J150">
         <v>36</v>
       </c>
-      <c r="K149">
+      <c r="K150">
         <v>29</v>
       </c>
-      <c r="L149">
+      <c r="L150">
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="O150">
+    <row r="151" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="O151">
         <v>1246</v>
       </c>
-      <c r="P150" t="s">
+      <c r="P151" t="s">
         <v>462</v>
       </c>
-      <c r="Q150" t="s">
+      <c r="Q151" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="152" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H152" t="s">
+    <row r="153" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H153" t="s">
         <v>377</v>
       </c>
-      <c r="I152">
+      <c r="I153">
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="I155" t="s">
+    <row r="156" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="I156" t="s">
         <v>464</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>